--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="12510" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -136,25 +136,31 @@
     <t>string</t>
   </si>
   <si>
+    <t>神圣狂斩</t>
+  </si>
+  <si>
+    <t>神圣破魂</t>
+  </si>
+  <si>
+    <t>神圣血刃</t>
+  </si>
+  <si>
+    <t>神圣屠龙</t>
+  </si>
+  <si>
+    <t>神圣倚天</t>
+  </si>
+  <si>
+    <t>神圣天命</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>神圣怒斩</t>
   </si>
   <si>
     <t>神圣噬魂</t>
-  </si>
-  <si>
-    <t>神圣血饮</t>
-  </si>
-  <si>
-    <t>神圣屠龙</t>
-  </si>
-  <si>
-    <t>神圣倚天</t>
-  </si>
-  <si>
-    <t>神圣命运</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1413,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:G5 C3:C5 D4:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1532,7 +1538,7 @@
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1558,7 +1564,7 @@
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1584,7 +1590,7 @@
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1610,7 +1616,7 @@
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1636,7 +1642,7 @@
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -1662,7 +1668,7 @@
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>16</v>
@@ -1817,7 +1823,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:G5 C3:C5 D4:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12510" windowHeight="9120"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
-    <sheet name="定制" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,39 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 神圣套</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +67,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Part</t>
   </si>
   <si>
@@ -109,7 +79,10 @@
     <t>Level</t>
   </si>
   <si>
-    <t>品质</t>
+    <t>StartQuality</t>
+  </si>
+  <si>
+    <t>EndQuality</t>
   </si>
   <si>
     <t>词条</t>
@@ -121,9 +94,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Quality</t>
-  </si>
-  <si>
     <t>RuneId</t>
   </si>
   <si>
@@ -154,13 +124,58 @@
     <t>神圣天命</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>神圣怒斩</t>
-  </si>
-  <si>
-    <t>神圣噬魂</t>
+    <t>传奇狂斩</t>
+  </si>
+  <si>
+    <t>传奇破魂</t>
+  </si>
+  <si>
+    <t>传奇血刃</t>
+  </si>
+  <si>
+    <t>传奇屠龙</t>
+  </si>
+  <si>
+    <t>传奇倚天</t>
+  </si>
+  <si>
+    <t>传奇天命</t>
+  </si>
+  <si>
+    <t>不朽狂斩</t>
+  </si>
+  <si>
+    <t>不朽破魂</t>
+  </si>
+  <si>
+    <t>不朽血刃</t>
+  </si>
+  <si>
+    <t>不朽屠龙</t>
+  </si>
+  <si>
+    <t>不朽倚天</t>
+  </si>
+  <si>
+    <t>不朽天命</t>
+  </si>
+  <si>
+    <t>永恒狂斩</t>
+  </si>
+  <si>
+    <t>永恒破魂</t>
+  </si>
+  <si>
+    <t>永恒血刃</t>
+  </si>
+  <si>
+    <t>永恒屠龙</t>
+  </si>
+  <si>
+    <t>永恒倚天</t>
+  </si>
+  <si>
+    <t>永恒天命</t>
   </si>
 </sst>
 </file>
@@ -1130,28 +1145,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="12.25" customWidth="1"/>
-    <col min="11" max="16371" width="9" style="2"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="12.25" customWidth="1"/>
+    <col min="13" max="16373" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1178,12 +1193,18 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1198,632 +1219,835 @@
         <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="L4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>13</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>16</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>-1</v>
+      </c>
+      <c r="L7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>17</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>-1</v>
+      </c>
+      <c r="L8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>18</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>-1</v>
+      </c>
+      <c r="L9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>19</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>-1</v>
+      </c>
+      <c r="L10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>-1</v>
+      </c>
+      <c r="L11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1007</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>-1</v>
+      </c>
+      <c r="L13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1008</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <v>-1</v>
+      </c>
+      <c r="L14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>1009</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>-1</v>
+      </c>
+      <c r="L15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>1010</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>-1</v>
+      </c>
+      <c r="L16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>1011</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>-1</v>
+      </c>
+      <c r="L17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>1012</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>6</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C20">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>1013</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <v>-1</v>
+      </c>
+      <c r="L20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C21">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>1014</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>7</v>
+      </c>
+      <c r="K21">
+        <v>-1</v>
+      </c>
+      <c r="L21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>1015</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <v>-1</v>
+      </c>
+      <c r="L22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>1016</v>
+      </c>
+      <c r="G23" s="1">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>7</v>
+      </c>
+      <c r="K23">
+        <v>-1</v>
+      </c>
+      <c r="L23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C24">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>1017</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>7</v>
+      </c>
+      <c r="K24">
+        <v>-1</v>
+      </c>
+      <c r="L24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C25">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>1018</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25">
+        <v>-1</v>
+      </c>
+      <c r="L25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C27">
         <v>19</v>
       </c>
-      <c r="E11">
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>1019</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>8</v>
+      </c>
+      <c r="K27">
+        <v>-1</v>
+      </c>
+      <c r="L27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C28">
         <v>20</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>-1</v>
-      </c>
-      <c r="I11">
-        <v>-1</v>
-      </c>
-      <c r="J11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12"/>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13"/>
-    </row>
-    <row r="14" spans="3:6">
-      <c r="C14"/>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="3:6">
-      <c r="C15"/>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17"/>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>1020</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>8</v>
+      </c>
+      <c r="K28">
+        <v>-1</v>
+      </c>
+      <c r="L28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C29">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>1021</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="K29">
+        <v>-1</v>
+      </c>
+      <c r="L29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C30">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>1022</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>8</v>
+      </c>
+      <c r="K30">
+        <v>-1</v>
+      </c>
+      <c r="L30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C31">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>1023</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>8</v>
+      </c>
+      <c r="K31">
+        <v>-1</v>
+      </c>
+      <c r="L31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>1024</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>8</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
+        <v>-1</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:G5 C3:C5 D4:D5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:XFB19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="12.25" customWidth="1"/>
-    <col min="11" max="16371" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C6">
-        <v>1000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C7">
-        <v>1000002</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>10024</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C8">
-        <v>1000003</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>10038</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C9">
-        <v>1000004</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C10">
-        <v>1000005</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>15</v>
-      </c>
-      <c r="J10">
-        <v>10024</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C11">
-        <v>1000006</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>16</v>
-      </c>
-      <c r="J11">
-        <v>10038</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="6:6">
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="6:6">
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="3:16382">
-      <c r="C14"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="XER14"/>
-      <c r="XES14"/>
-      <c r="XET14"/>
-      <c r="XEU14"/>
-      <c r="XEV14"/>
-      <c r="XEW14"/>
-      <c r="XEX14"/>
-      <c r="XEY14"/>
-      <c r="XEZ14"/>
-      <c r="XFA14"/>
-      <c r="XFB14"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="3:16382">
-      <c r="C15"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="XER15"/>
-      <c r="XES15"/>
-      <c r="XET15"/>
-      <c r="XEU15"/>
-      <c r="XEV15"/>
-      <c r="XEW15"/>
-      <c r="XEX15"/>
-      <c r="XEY15"/>
-      <c r="XEZ15"/>
-      <c r="XFA15"/>
-      <c r="XFB15"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="3:16382">
-      <c r="C16"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16"/>
-      <c r="G16" s="1"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="XER16"/>
-      <c r="XES16"/>
-      <c r="XET16"/>
-      <c r="XEU16"/>
-      <c r="XEV16"/>
-      <c r="XEW16"/>
-      <c r="XEX16"/>
-      <c r="XEY16"/>
-      <c r="XEZ16"/>
-      <c r="XFA16"/>
-      <c r="XFB16"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="3:16382">
-      <c r="C17"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17"/>
-      <c r="G17" s="1"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="XER17"/>
-      <c r="XES17"/>
-      <c r="XET17"/>
-      <c r="XEU17"/>
-      <c r="XEV17"/>
-      <c r="XEW17"/>
-      <c r="XEX17"/>
-      <c r="XEY17"/>
-      <c r="XEZ17"/>
-      <c r="XFA17"/>
-      <c r="XFB17"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="3:16382">
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18"/>
-      <c r="G18" s="1"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-      <c r="XER18"/>
-      <c r="XES18"/>
-      <c r="XET18"/>
-      <c r="XEU18"/>
-      <c r="XEV18"/>
-      <c r="XEW18"/>
-      <c r="XEX18"/>
-      <c r="XEY18"/>
-      <c r="XEZ18"/>
-      <c r="XFA18"/>
-      <c r="XFB18"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="3:16382">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19"/>
-      <c r="G19" s="1"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="XER19"/>
-      <c r="XES19"/>
-      <c r="XET19"/>
-      <c r="XEU19"/>
-      <c r="XEV19"/>
-      <c r="XEW19"/>
-      <c r="XEX19"/>
-      <c r="XEY19"/>
-      <c r="XEZ19"/>
-      <c r="XFA19"/>
-      <c r="XFB19"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:G5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>永恒天命</t>
+  </si>
+  <si>
+    <t>神圣怒斩</t>
+  </si>
+  <si>
+    <t>神圣噬魂</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2045,6 +2051,198 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="48" spans="3:12">
+      <c r="C48">
+        <v>1000001</v>
+      </c>
+      <c r="D48" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>15</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>14</v>
+      </c>
+      <c r="L48">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
+      <c r="C49">
+        <v>1000002</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>15</v>
+      </c>
+      <c r="L49">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
+      <c r="C50">
+        <v>1000003</v>
+      </c>
+      <c r="D50" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>16</v>
+      </c>
+      <c r="L50">
+        <v>10038</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
+      <c r="C51">
+        <v>1000004</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>16</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>14</v>
+      </c>
+      <c r="L51">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
+      <c r="C52">
+        <v>1000005</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>16</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>15</v>
+      </c>
+      <c r="L52">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12">
+      <c r="C53">
+        <v>1000006</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>16</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>16</v>
+      </c>
+      <c r="L53">
+        <v>10038</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -1164,11 +1164,11 @@
     <col min="13" max="16373" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:2">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:2">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C6">
         <v>1</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C7">
         <v>2</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C8">
         <v>3</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C9">
         <v>4</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C10">
         <v>5</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="11" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C11">
         <v>6</v>
       </c>
@@ -1466,10 +1466,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="7:7">
+    <row r="12" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="G12" s="1"/>
     </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="13" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C13">
         <v>7</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="14" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C14">
         <v>8</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="15" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C15">
         <v>9</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="16" customFormat="1" ht="27" customHeight="1" spans="1:12">
       <c r="C16">
         <v>10</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="27" customHeight="1" spans="7:7">
+    <row r="19" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="G19" s="1"/>
     </row>
     <row r="20" customFormat="1" ht="27" customHeight="1" spans="3:12">
@@ -1856,7 +1856,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="27" customHeight="1" spans="7:7">
+    <row r="26" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="G26" s="1"/>
     </row>
     <row r="27" customFormat="1" ht="27" customHeight="1" spans="3:12">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -77,12 +77,6 @@
   </si>
   <si>
     <t>Level</t>
-  </si>
-  <si>
-    <t>StartQuality</t>
-  </si>
-  <si>
-    <t>EndQuality</t>
   </si>
   <si>
     <t>词条</t>
@@ -1151,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1160,19 +1154,19 @@
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="12.25" customWidth="1"/>
-    <col min="13" max="16373" width="9" style="2"/>
+    <col min="9" max="10" width="12.25" customWidth="1"/>
+    <col min="11" max="16371" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:12">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1199,18 +1193,12 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1228,58 +1216,46 @@
         <v>5</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="1:10">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1294,24 +1270,18 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>-1</v>
-      </c>
-      <c r="L6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1326,24 +1296,18 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>-1</v>
-      </c>
-      <c r="L7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1358,24 +1322,18 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>-1</v>
-      </c>
-      <c r="L8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1390,24 +1348,18 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
-        <v>-1</v>
-      </c>
-      <c r="L9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1422,24 +1374,18 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J10">
-        <v>4</v>
-      </c>
-      <c r="K10">
-        <v>-1</v>
-      </c>
-      <c r="L10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1454,27 +1400,21 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J11">
-        <v>4</v>
-      </c>
-      <c r="K11">
-        <v>-1</v>
-      </c>
-      <c r="L11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="G12" s="1"/>
     </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="1:12">
+    <row r="13" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1489,24 +1429,18 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J13">
-        <v>6</v>
-      </c>
-      <c r="K13">
-        <v>-1</v>
-      </c>
-      <c r="L13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C14">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1521,24 +1455,18 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J14">
-        <v>6</v>
-      </c>
-      <c r="K14">
-        <v>-1</v>
-      </c>
-      <c r="L14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C15">
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1553,24 +1481,18 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J15">
-        <v>6</v>
-      </c>
-      <c r="K15">
-        <v>-1</v>
-      </c>
-      <c r="L15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="27" customHeight="1" spans="1:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C16">
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1585,24 +1507,18 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J16">
-        <v>6</v>
-      </c>
-      <c r="K16">
-        <v>-1</v>
-      </c>
-      <c r="L16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C17">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1617,24 +1533,18 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J17">
-        <v>6</v>
-      </c>
-      <c r="K17">
-        <v>-1</v>
-      </c>
-      <c r="L17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C18">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1649,27 +1559,21 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J18">
-        <v>6</v>
-      </c>
-      <c r="K18">
-        <v>-1</v>
-      </c>
-      <c r="L18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="G19" s="1"/>
     </row>
-    <row r="20" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="20" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C20">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1684,24 +1588,18 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J20">
-        <v>7</v>
-      </c>
-      <c r="K20">
-        <v>-1</v>
-      </c>
-      <c r="L20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C21">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1716,24 +1614,18 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J21">
-        <v>7</v>
-      </c>
-      <c r="K21">
-        <v>-1</v>
-      </c>
-      <c r="L21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C22">
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -1748,24 +1640,18 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J22">
-        <v>7</v>
-      </c>
-      <c r="K22">
-        <v>-1</v>
-      </c>
-      <c r="L22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C23">
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -1780,24 +1666,18 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J23">
-        <v>7</v>
-      </c>
-      <c r="K23">
-        <v>-1</v>
-      </c>
-      <c r="L23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C24">
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -1812,24 +1692,18 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J24">
-        <v>7</v>
-      </c>
-      <c r="K24">
-        <v>-1</v>
-      </c>
-      <c r="L24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C25">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1844,27 +1718,21 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J25">
-        <v>7</v>
-      </c>
-      <c r="K25">
-        <v>-1</v>
-      </c>
-      <c r="L25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="G26" s="1"/>
     </row>
-    <row r="27" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="27" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C27">
         <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -1879,24 +1747,18 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J27">
-        <v>8</v>
-      </c>
-      <c r="K27">
-        <v>-1</v>
-      </c>
-      <c r="L27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C28">
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -1911,24 +1773,18 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J28">
-        <v>8</v>
-      </c>
-      <c r="K28">
-        <v>-1</v>
-      </c>
-      <c r="L28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C29">
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E29">
         <v>4</v>
@@ -1943,24 +1799,18 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J29">
-        <v>8</v>
-      </c>
-      <c r="K29">
-        <v>-1</v>
-      </c>
-      <c r="L29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C30">
         <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -1975,24 +1825,18 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J30">
-        <v>8</v>
-      </c>
-      <c r="K30">
-        <v>-1</v>
-      </c>
-      <c r="L30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C31">
         <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E31">
         <v>4</v>
@@ -2007,24 +1851,18 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J31">
-        <v>8</v>
-      </c>
-      <c r="K31">
-        <v>-1</v>
-      </c>
-      <c r="L31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" ht="27" customHeight="1" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C32">
         <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E32">
         <v>4</v>
@@ -2039,24 +1877,18 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J32">
-        <v>8</v>
-      </c>
-      <c r="K32">
-        <v>-1</v>
-      </c>
-      <c r="L32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="3:12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10">
       <c r="C48">
         <v>1000001</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2070,25 +1902,19 @@
       <c r="H48">
         <v>1</v>
       </c>
-      <c r="I48">
-        <v>1</v>
+      <c r="I48" s="1">
+        <v>14</v>
       </c>
       <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>14</v>
-      </c>
-      <c r="L48">
         <v>10010</v>
       </c>
     </row>
-    <row r="49" spans="3:12">
+    <row r="49" spans="3:10">
       <c r="C49">
         <v>1000002</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2103,24 +1929,18 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49">
-        <v>15</v>
-      </c>
-      <c r="L49">
         <v>10024</v>
       </c>
     </row>
-    <row r="50" spans="3:12">
+    <row r="50" spans="3:10">
       <c r="C50">
         <v>1000003</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -2135,24 +1955,18 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <v>16</v>
-      </c>
-      <c r="L50">
         <v>10038</v>
       </c>
     </row>
-    <row r="51" spans="3:12">
+    <row r="51" spans="3:10">
       <c r="C51">
         <v>1000004</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -2166,25 +1980,19 @@
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51">
-        <v>1</v>
+      <c r="I51" s="1">
+        <v>14</v>
       </c>
       <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>14</v>
-      </c>
-      <c r="L51">
         <v>10010</v>
       </c>
     </row>
-    <row r="52" spans="3:12">
+    <row r="52" spans="3:10">
       <c r="C52">
         <v>1000005</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -2199,24 +2007,18 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>15</v>
-      </c>
-      <c r="L52">
         <v>10024</v>
       </c>
     </row>
-    <row r="53" spans="3:12">
+    <row r="53" spans="3:10">
       <c r="C53">
         <v>1000006</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -2231,15 +2033,9 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>16</v>
-      </c>
-      <c r="L53">
         <v>10038</v>
       </c>
     </row>
